--- a/TestData/LV_T1513_ClientGiftPre_ApprovalPage_AddingaRecipientToTheSelectedRecipientSection.xlsx
+++ b/TestData/LV_T1513_ClientGiftPre_ApprovalPage_AddingaRecipientToTheSelectedRecipientSection.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25EE2628-C826-4D4A-BC50-BC1E0C41ABA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C690E86C-C79A-4F32-B599-282C3A102479}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="5" r:id="rId1"/>
@@ -136,9 +136,6 @@
     <t>ContactName</t>
   </si>
   <si>
-    <t>Test External</t>
-  </si>
-  <si>
     <t>CongratulationsMsg</t>
   </si>
   <si>
@@ -157,9 +154,6 @@
     <t>U.S. Dollar</t>
   </si>
   <si>
-    <t>Giorgia Cardia</t>
-  </si>
-  <si>
     <t>StandardTestCompany</t>
   </si>
   <si>
@@ -202,10 +196,16 @@
     <t>Gift Requests</t>
   </si>
   <si>
-    <t>External</t>
-  </si>
-  <si>
-    <t>Test</t>
+    <t>Olivia Ricketts</t>
+  </si>
+  <si>
+    <t>Giftlog Contact</t>
+  </si>
+  <si>
+    <t>Contact</t>
+  </si>
+  <si>
+    <t>Giftlog</t>
   </si>
 </sst>
 </file>
@@ -544,12 +544,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -568,12 +568,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -588,12 +588,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -624,7 +624,7 @@
         <v>23</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>25</v>
@@ -633,7 +633,7 @@
         <v>26</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>28</v>
@@ -651,7 +651,7 @@
         <v>22</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
@@ -659,16 +659,16 @@
         <v>24</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D2" t="s">
         <v>27</v>
       </c>
       <c r="E2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F2" t="s">
         <v>29</v>
@@ -677,16 +677,16 @@
         <v>31</v>
       </c>
       <c r="H2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I2" t="s">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="J2" t="s">
         <v>21</v>
       </c>
       <c r="K2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -846,82 +846,82 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B5" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>34</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>34</v>
+        <v>55</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>34</v>
+        <v>55</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>34</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
@@ -931,7 +931,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>34</v>
+        <v>55</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
@@ -959,27 +959,27 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>

--- a/TestData/LV_T1513_ClientGiftPre_ApprovalPage_AddingaRecipientToTheSelectedRecipientSection.xlsx
+++ b/TestData/LV_T1513_ClientGiftPre_ApprovalPage_AddingaRecipientToTheSelectedRecipientSection.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C690E86C-C79A-4F32-B599-282C3A102479}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD728680-1F6E-4117-807E-31CD57958436}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="5" r:id="rId1"/>
@@ -196,9 +196,6 @@
     <t>Gift Requests</t>
   </si>
   <si>
-    <t>Olivia Ricketts</t>
-  </si>
-  <si>
     <t>Giftlog Contact</t>
   </si>
   <si>
@@ -206,6 +203,9 @@
   </si>
   <si>
     <t>Giftlog</t>
+  </si>
+  <si>
+    <t>Melissa Zatta</t>
   </si>
 </sst>
 </file>
@@ -549,7 +549,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -659,7 +659,7 @@
         <v>24</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>50</v>
@@ -680,7 +680,7 @@
         <v>40</v>
       </c>
       <c r="I2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J2" t="s">
         <v>21</v>
@@ -886,22 +886,22 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
@@ -926,22 +926,22 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>

--- a/TestData/LV_T1513_ClientGiftPre_ApprovalPage_AddingaRecipientToTheSelectedRecipientSection.xlsx
+++ b/TestData/LV_T1513_ClientGiftPre_ApprovalPage_AddingaRecipientToTheSelectedRecipientSection.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F9A146E-EF22-4AFB-B9DA-6930764CEA05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3A9E9A9-9FC3-44F4-991D-64BFA2B74D88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="708" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="5" r:id="rId1"/>
@@ -537,17 +537,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>57</v>
       </c>
@@ -561,17 +561,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C1A4194-07F7-4B4A-B892-397CC42812D5}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>52</v>
       </c>
@@ -584,14 +584,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C302D36C-1AE9-423E-B7FA-38417851D3D4}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>53</v>
       </c>
@@ -604,21 +604,21 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:K2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.109375" customWidth="1"/>
-    <col min="6" max="6" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="20.33203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.5546875" customWidth="1"/>
+    <col min="1" max="1" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.140625" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>23</v>
       </c>
@@ -653,7 +653,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>24</v>
       </c>
@@ -697,13 +697,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B10"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="39.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="43.5546875" customWidth="1"/>
+    <col min="1" max="1" width="39.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -711,7 +711,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -719,7 +719,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -727,7 +727,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -735,13 +735,13 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>6</v>
       </c>
       <c r="B5" s="2"/>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -749,13 +749,13 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
       <c r="B7" s="2"/>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -763,13 +763,13 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>11</v>
       </c>
       <c r="B9" s="2"/>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -786,13 +786,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="33.109375" customWidth="1"/>
-    <col min="2" max="2" width="26.44140625" customWidth="1"/>
+    <col min="1" max="1" width="33.140625" customWidth="1"/>
+    <col min="2" max="2" width="26.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -800,7 +800,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -808,7 +808,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -816,12 +816,12 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -836,14 +836,14 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:B17"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:C17"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="32.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="34.88671875" customWidth="1"/>
+    <col min="1" max="1" width="32.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>41</v>
       </c>
@@ -851,7 +851,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>43</v>
       </c>
@@ -859,86 +859,86 @@
         <v>46</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>40</v>
       </c>
       <c r="B3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C3" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>40</v>
       </c>
       <c r="B4" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>40</v>
       </c>
-      <c r="B5" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>55</v>
       </c>
@@ -951,32 +951,32 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AAB7F185-1A7D-49DA-8200-6FA66E3E484A}">
   <dimension ref="A1:A5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="36.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="36.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>49</v>
       </c>

--- a/TestData/LV_T1513_ClientGiftPre_ApprovalPage_AddingaRecipientToTheSelectedRecipientSection.xlsx
+++ b/TestData/LV_T1513_ClientGiftPre_ApprovalPage_AddingaRecipientToTheSelectedRecipientSection.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3A9E9A9-9FC3-44F4-991D-64BFA2B74D88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{075083CB-9FEC-4DC8-8779-D65AEE84D74F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-23148" yWindow="708" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -836,14 +836,14 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="32.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="34.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>41</v>
       </c>
@@ -851,7 +851,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>43</v>
       </c>
@@ -859,81 +859,81 @@
         <v>46</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>40</v>
       </c>
       <c r="B3" t="s">
-        <v>48</v>
-      </c>
-      <c r="C3" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>40</v>
       </c>
       <c r="B4" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>56</v>
       </c>

--- a/TestData/LV_T1513_ClientGiftPre_ApprovalPage_AddingaRecipientToTheSelectedRecipientSection.xlsx
+++ b/TestData/LV_T1513_ClientGiftPre_ApprovalPage_AddingaRecipientToTheSelectedRecipientSection.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{075083CB-9FEC-4DC8-8779-D65AEE84D74F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC0CD8B4-CBF2-47E1-A8FD-1A4457A7EA4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="708" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="5" r:id="rId1"/>
@@ -142,9 +142,6 @@
     <t>Congratulations</t>
   </si>
   <si>
-    <t>StdUser</t>
-  </si>
-  <si>
     <t>SubmittedFor</t>
   </si>
   <si>
@@ -205,7 +202,10 @@
     <t>Giftlog</t>
   </si>
   <si>
-    <t>Melissa Zatta</t>
+    <t>Julie Carthane</t>
+  </si>
+  <si>
+    <t>CF FinancialUser</t>
   </si>
 </sst>
 </file>
@@ -544,12 +544,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>36</v>
+        <v>57</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>57</v>
+      <c r="A2" t="s">
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -568,12 +568,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -588,12 +588,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -623,7 +623,7 @@
         <v>23</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>25</v>
@@ -632,7 +632,7 @@
         <v>26</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>28</v>
@@ -657,17 +657,17 @@
       <c r="A2" t="s">
         <v>24</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>57</v>
+      <c r="B2" t="s">
+        <v>56</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D2" t="s">
         <v>27</v>
       </c>
       <c r="E2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F2" t="s">
         <v>29</v>
@@ -676,10 +676,10 @@
         <v>31</v>
       </c>
       <c r="H2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J2" t="s">
         <v>21</v>
@@ -845,102 +845,102 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>41</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -958,27 +958,27 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
